--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33016023-156E-4E75-98A9-785F0EE7F82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A942DAA848F5BFCD998A2B514E77835C70D8467A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF3BFE69-6491-4199-BDFF-E294590E9809}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 09-09-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 14-09-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -458,9 +458,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -532,7 +532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -555,7 +555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -598,7 +598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -624,7 +624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -670,7 +670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -747,7 +747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>29</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A942DAA848F5BFCD998A2B514E77835C70D8467A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF3BFE69-6491-4199-BDFF-E294590E9809}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A942DAA848F5BFCD998A2B1E66768E8470D8467A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67C35B1F-5D87-44C2-9534-6D1298345314}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A942DAA848F5BFCD998A2B1E66768E8470D8467A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67C35B1F-5D87-44C2-9534-6D1298345314}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42922F2-1A60-4930-8B15-6CB4233E8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -458,9 +458,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -532,7 +532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -555,7 +555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -598,7 +598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -624,7 +624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -670,7 +670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -747,7 +747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42922F2-1A60-4930-8B15-6CB4233E8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC33564-ACF4-4633-BBE3-95D96CE685B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 14-09-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 17-09-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="31">
   <si>
     <t>Standard</t>
   </si>
@@ -458,9 +458,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -532,7 +532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -555,7 +555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -598,7 +598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -618,13 +618,13 @@
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -670,7 +670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -690,13 +690,13 @@
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -747,7 +747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -765,9 +765,6 @@
       </c>
       <c r="F14" t="s">
         <v>11</v>
-      </c>
-      <c r="G14" t="s">
-        <v>21</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC33564-ACF4-4633-BBE3-95D96CE685B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD7A384-4125-4B1D-9CAB-18CF85E96628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD7A384-4125-4B1D-9CAB-18CF85E96628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_CCF298A548F5BFCD998A2B1D86B5AAA471D8F6AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF73A441-9175-4CEC-89E5-76F24163B2D1}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 17-09-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 18-09-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -458,9 +458,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -532,7 +532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -555,7 +555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -598,7 +598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -624,7 +624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -670,7 +670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -747,7 +747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>29</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_CCF298A548F5BFCD998A2B1D86B5AAA471D8F6AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF73A441-9175-4CEC-89E5-76F24163B2D1}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_CCF298A548F5BFCD998A2B5F5637A29070D8F6AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30952DAB-93B7-42AF-8C8E-8A72D315AEBB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 18-09-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 21-09-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_CCF298A548F5BFCD998A2B5F5637A29070D8F6AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30952DAB-93B7-42AF-8C8E-8A72D315AEBB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD084D5D-0467-4235-9C32-D709245AC489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -458,9 +458,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -532,7 +532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -555,7 +555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -598,7 +598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -624,7 +624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -670,7 +670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -747,7 +747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD084D5D-0467-4235-9C32-D709245AC489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50765E6A-50AF-47CD-81E9-2821A6C235FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 21-09-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 22-09-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50765E6A-50AF-47CD-81E9-2821A6C235FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414DA2F5-D15D-4E8B-9DCF-618D529AEC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414DA2F5-D15D-4E8B-9DCF-618D529AEC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06686D67-0D78-46A4-B1D1-3EC0F3430B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 22-09-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 23-09-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06686D67-0D78-46A4-B1D1-3EC0F3430B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_CCF298A548F5BFCD998A2B1F9EB78DBC71D8F6AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9026747-BB47-4CC2-890B-772B8C0B652D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -458,9 +458,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -532,7 +532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -555,7 +555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -598,7 +598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -624,7 +624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -670,7 +670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -747,7 +747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>29</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_CCF298A548F5BFCD998A2B1F9EB78DBC71D8F6AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9026747-BB47-4CC2-890B-772B8C0B652D}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_CCF298A548F5BFCD998A2BE44EF49E6870D8F6AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DEB97B0-BCC4-47F5-8B78-B87A880ADF87}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 23-09-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 24-09-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_CCF298A548F5BFCD998A2BE44EF49E6870D8F6AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DEB97B0-BCC4-47F5-8B78-B87A880ADF87}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_CCF298A548F5BFCD998A2B909E35B27E71D8F6AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F301B44F-E6FA-4BEF-8098-F4D12B4BE611}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_CCF298A548F5BFCD998A2B909E35B27E71D8F6AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F301B44F-E6FA-4BEF-8098-F4D12B4BE611}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36ADDE58-9308-4D06-96C4-FE32DC66FBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 24-09-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 28-09-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -458,9 +458,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -532,7 +532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -555,7 +555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -598,7 +598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -624,7 +624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -670,7 +670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -747,7 +747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36ADDE58-9308-4D06-96C4-FE32DC66FBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_CCF298A548F5BFCD998A2BCF66F1AEC670D8F6AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDC03FE8-0D4A-484F-95CA-6902F69CA158}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 28-09-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 02-10-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -458,9 +458,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -532,7 +532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -555,7 +555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -598,7 +598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -624,7 +624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -670,7 +670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -747,7 +747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>29</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414DA2F5-D15D-4E8B-9DCF-618D529AEC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A38E18-6BC8-42EE-A66A-C4A6A2FF8F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 22-09-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 07-10-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_CCF298A548F5BFCD998A2BCF66F1AEC670D8F6AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDC03FE8-0D4A-484F-95CA-6902F69CA158}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8EBF6D8-F98F-4F23-907C-D09B27829ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 02-10-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 07-10-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -458,9 +458,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -532,7 +532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -555,7 +555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -598,7 +598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -624,7 +624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -670,7 +670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -747,7 +747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8EBF6D8-F98F-4F23-907C-D09B27829ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9AD25FCD8EF8B2BA92673801871D8B74E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A3C1F34-2F50-4D74-814B-DEEBB6AD347C}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 07-10-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 08-10-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="31">
   <si>
     <t>Standard</t>
   </si>
@@ -505,6 +505,9 @@
       <c r="F2" t="s">
         <v>11</v>
       </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
@@ -528,6 +531,9 @@
       <c r="F3" t="s">
         <v>11</v>
       </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
       <c r="H3" t="s">
         <v>11</v>
       </c>
@@ -551,6 +557,9 @@
       <c r="F4" t="s">
         <v>11</v>
       </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
@@ -643,6 +652,9 @@
       <c r="F8" t="s">
         <v>11</v>
       </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
@@ -664,6 +676,9 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
         <v>11</v>
       </c>
       <c r="H9" t="s">

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9AD25FCD8EF8B2BA92673801871D8B74E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A3C1F34-2F50-4D74-814B-DEEBB6AD347C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BC16E1-BCA2-4FEA-B922-DD78FCC4845E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 08-10-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 09-10-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BC16E1-BCA2-4FEA-B922-DD78FCC4845E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E90C7C4-C3D0-486E-9512-665DBE1F6349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E90C7C4-C3D0-486E-9512-665DBE1F6349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9AD25FCD8EF8B2B13AEB4AFD870D8B74E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86F6BCCF-5FEC-4BDD-AE4C-19414A2CF11B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 09-10-2026'!$A$1:$H$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 23-10-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
